--- a/results/data/semih_vanilla_dqn_experiment_results.xlsx
+++ b/results/data/semih_vanilla_dqn_experiment_results.xlsx
@@ -750,190 +750,190 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>95.2</v>
+        <v>137.6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.993325909419153</v>
+        <v>5.40740233383831</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>144.6</v>
       </c>
       <c r="E2" t="n">
-        <v>3.40587727318528</v>
+        <v>5.003998401278722</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>146.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32379000772445</v>
+        <v>7.483982896827063</v>
       </c>
       <c r="H2" t="n">
-        <v>96.3</v>
+        <v>150.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.163858403911275</v>
+        <v>7.867019766086774</v>
       </c>
       <c r="J2" t="n">
-        <v>97.3</v>
+        <v>150</v>
       </c>
       <c r="K2" t="n">
-        <v>2.531797780234433</v>
+        <v>5.830951894845301</v>
       </c>
       <c r="L2" t="n">
-        <v>95.2</v>
+        <v>147.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.925747767665559</v>
+        <v>8.459314393022639</v>
       </c>
       <c r="N2" t="n">
-        <v>96.5</v>
+        <v>147.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3.556683848755748</v>
+        <v>6.797793759742936</v>
       </c>
       <c r="P2" t="n">
-        <v>99.7</v>
+        <v>177</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.495553358597805</v>
+        <v>40.99268227379126</v>
       </c>
       <c r="R2" t="n">
-        <v>101.5</v>
+        <v>181.5</v>
       </c>
       <c r="S2" t="n">
-        <v>4.716990566028302</v>
+        <v>49.94046455530825</v>
       </c>
       <c r="T2" t="n">
-        <v>102.8</v>
+        <v>188.9</v>
       </c>
       <c r="U2" t="n">
-        <v>5.600000000000001</v>
+        <v>52.49466639573968</v>
       </c>
       <c r="V2" t="n">
-        <v>93.2</v>
+        <v>179.1</v>
       </c>
       <c r="W2" t="n">
-        <v>24.8708664907357</v>
+        <v>57.53511970961735</v>
       </c>
       <c r="X2" t="n">
-        <v>94.90000000000001</v>
+        <v>246.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.09362468835461</v>
+        <v>87.62328457664664</v>
       </c>
       <c r="Z2" t="n">
-        <v>100.2</v>
+        <v>195.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.70721785835617</v>
+        <v>27.69566753122228</v>
       </c>
       <c r="AB2" t="n">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="AC2" t="n">
-        <v>28.78888674471453</v>
+        <v>65.5469297526589</v>
       </c>
       <c r="AD2" t="n">
-        <v>86.3</v>
+        <v>195.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>33.16338342208165</v>
+        <v>46.25159456710655</v>
       </c>
       <c r="AF2" t="n">
-        <v>84.09999999999999</v>
+        <v>217.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>30.17764072952026</v>
+        <v>55.30650956261839</v>
       </c>
       <c r="AH2" t="n">
-        <v>64.8</v>
+        <v>211</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.06584563615185</v>
+        <v>50.63398068491159</v>
       </c>
       <c r="AJ2" t="n">
-        <v>66.3</v>
+        <v>240.8</v>
       </c>
       <c r="AK2" t="n">
-        <v>31.24435949095453</v>
+        <v>68.30929658545752</v>
       </c>
       <c r="AL2" t="n">
-        <v>58.9</v>
+        <v>240.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>26.94605722550147</v>
+        <v>61.84949474328792</v>
       </c>
       <c r="AN2" t="n">
-        <v>53</v>
+        <v>224.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>18.71897433087614</v>
+        <v>51.8814995928221</v>
       </c>
       <c r="AP2" t="n">
-        <v>45.3</v>
+        <v>230.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.491987158875422</v>
+        <v>59.56181662776917</v>
       </c>
       <c r="AR2" t="n">
-        <v>52.3</v>
+        <v>223.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>20.60121355648739</v>
+        <v>50.84535377003488</v>
       </c>
       <c r="AT2" t="n">
-        <v>46.1</v>
+        <v>223.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.256102834535695</v>
+        <v>52.65130577678012</v>
       </c>
       <c r="AV2" t="n">
-        <v>52</v>
+        <v>226.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>20.08979840615629</v>
+        <v>41.00841377083488</v>
       </c>
       <c r="AX2" t="n">
-        <v>46.5</v>
+        <v>220.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.5</v>
+        <v>42.50235287604676</v>
       </c>
       <c r="AZ2" t="n">
-        <v>46</v>
+        <v>234.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.144761058952722</v>
+        <v>43.11623824036601</v>
       </c>
       <c r="BB2" t="n">
-        <v>51.1</v>
+        <v>201.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.7</v>
+        <v>14.9829903557334</v>
       </c>
       <c r="BD2" t="n">
-        <v>47</v>
+        <v>241.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.049691346263317</v>
+        <v>64.3105745581549</v>
       </c>
       <c r="BF2" t="n">
-        <v>45.6</v>
+        <v>244.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.457641145488902</v>
+        <v>40.68709869233736</v>
       </c>
       <c r="BH2" t="n">
-        <v>48.9</v>
+        <v>246</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.672873534441392</v>
+        <v>52.95847429826505</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2243</v>
+        <v>6014.3</v>
       </c>
       <c r="BK2" t="n">
-        <v>74.76666666666665</v>
+        <v>200.4766666666667</v>
       </c>
     </row>
     <row r="3">
@@ -941,190 +941,190 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>93.90000000000001</v>
+        <v>140.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3.753664875824692</v>
+        <v>6.050619802962338</v>
       </c>
       <c r="D3" t="n">
-        <v>95.09999999999999</v>
+        <v>144.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.879236009777594</v>
+        <v>6.917369442208505</v>
       </c>
       <c r="F3" t="n">
-        <v>93.90000000000001</v>
+        <v>147.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.808914381037628</v>
+        <v>7.462573282722255</v>
       </c>
       <c r="H3" t="n">
-        <v>94.59999999999999</v>
+        <v>150.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.939387691339813</v>
+        <v>7.707788269017255</v>
       </c>
       <c r="J3" t="n">
-        <v>96</v>
+        <v>154.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.82842712474619</v>
+        <v>9.385627309881849</v>
       </c>
       <c r="L3" t="n">
-        <v>95.8</v>
+        <v>152.9</v>
       </c>
       <c r="M3" t="n">
-        <v>4.069397989875161</v>
+        <v>9.406912352095134</v>
       </c>
       <c r="N3" t="n">
-        <v>98.2</v>
+        <v>161.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.249615361854385</v>
+        <v>32.13113754600045</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>163.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.669047011971501</v>
+        <v>20.05218192616454</v>
       </c>
       <c r="R3" t="n">
-        <v>102.6</v>
+        <v>181.5</v>
       </c>
       <c r="S3" t="n">
-        <v>4.983974317750844</v>
+        <v>38.13462993133669</v>
       </c>
       <c r="T3" t="n">
-        <v>91.09999999999999</v>
+        <v>192.6</v>
       </c>
       <c r="U3" t="n">
-        <v>23.04538999453036</v>
+        <v>62.97809142868653</v>
       </c>
       <c r="V3" t="n">
-        <v>104.8</v>
+        <v>172.9</v>
       </c>
       <c r="W3" t="n">
-        <v>2.675817632051931</v>
+        <v>23.14497785697796</v>
       </c>
       <c r="X3" t="n">
-        <v>82.2</v>
+        <v>255.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>29.88578257298945</v>
+        <v>89.5613756035491</v>
       </c>
       <c r="Z3" t="n">
-        <v>83.7</v>
+        <v>222.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>30.39095260106205</v>
+        <v>70.92256340544947</v>
       </c>
       <c r="AB3" t="n">
-        <v>90.3</v>
+        <v>207.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>28.84805019407724</v>
+        <v>43.75442834731132</v>
       </c>
       <c r="AD3" t="n">
-        <v>84.59999999999999</v>
+        <v>186.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>31.93806506349437</v>
+        <v>38.31501011353122</v>
       </c>
       <c r="AF3" t="n">
-        <v>78.40000000000001</v>
+        <v>217.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>32.94905157967373</v>
+        <v>55.76522213709904</v>
       </c>
       <c r="AH3" t="n">
-        <v>64.90000000000001</v>
+        <v>200.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>29.22481822013611</v>
+        <v>33.02135672561017</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65.90000000000001</v>
+        <v>246.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>30.13453168708616</v>
+        <v>57.79065668427726</v>
       </c>
       <c r="AL3" t="n">
-        <v>66.7</v>
+        <v>215.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>31.03884662805627</v>
+        <v>60.01366511053962</v>
       </c>
       <c r="AN3" t="n">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="AO3" t="n">
-        <v>20.06489471689299</v>
+        <v>54.86893474453463</v>
       </c>
       <c r="AP3" t="n">
-        <v>52.1</v>
+        <v>242.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20.73378884815797</v>
+        <v>55.13111644071794</v>
       </c>
       <c r="AR3" t="n">
-        <v>66.90000000000001</v>
+        <v>240.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>31.18797845324381</v>
+        <v>55.63281405789213</v>
       </c>
       <c r="AT3" t="n">
-        <v>47.7</v>
+        <v>238.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.615549442140351</v>
+        <v>56.76451356261234</v>
       </c>
       <c r="AV3" t="n">
-        <v>46.3</v>
+        <v>256.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.368543856465402</v>
+        <v>47.58403093475793</v>
       </c>
       <c r="AX3" t="n">
-        <v>58.5</v>
+        <v>244.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>21.96474447836805</v>
+        <v>69.97456680823397</v>
       </c>
       <c r="AZ3" t="n">
-        <v>48.3</v>
+        <v>237.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.716180835212409</v>
+        <v>53.56827419284665</v>
       </c>
       <c r="BB3" t="n">
-        <v>46.3</v>
+        <v>247.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.124318125460257</v>
+        <v>53.82276470044994</v>
       </c>
       <c r="BD3" t="n">
-        <v>45.9</v>
+        <v>246.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.7</v>
+        <v>69.21278783577496</v>
       </c>
       <c r="BF3" t="n">
-        <v>49.3</v>
+        <v>255.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.550675634551167</v>
+        <v>54.3529208046817</v>
       </c>
       <c r="BH3" t="n">
-        <v>46.5</v>
+        <v>282.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.334523505985751</v>
+        <v>57.1951921056307</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2243.500000000001</v>
+        <v>6247.199999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>74.78333333333336</v>
+        <v>208.24</v>
       </c>
     </row>
     <row r="4">
@@ -1132,190 +1132,190 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>95.5</v>
+        <v>139.3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.539685019840059</v>
+        <v>6.723838189605696</v>
       </c>
       <c r="D4" t="n">
-        <v>95.2</v>
+        <v>145.6</v>
       </c>
       <c r="E4" t="n">
-        <v>3.682390527904394</v>
+        <v>6.696267617113283</v>
       </c>
       <c r="F4" t="n">
-        <v>93.7</v>
+        <v>148</v>
       </c>
       <c r="G4" t="n">
-        <v>2.934280150224243</v>
+        <v>7.085195833567341</v>
       </c>
       <c r="H4" t="n">
-        <v>94.59999999999999</v>
+        <v>149.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.154065922853801</v>
+        <v>11.88107739222332</v>
       </c>
       <c r="J4" t="n">
-        <v>96.3</v>
+        <v>147.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.794637722496424</v>
+        <v>4.220189569201838</v>
       </c>
       <c r="L4" t="n">
-        <v>95</v>
+        <v>177.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.741657386773941</v>
+        <v>51.45638930200991</v>
       </c>
       <c r="N4" t="n">
-        <v>97.2</v>
+        <v>151.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.429285639896449</v>
+        <v>4.467661580737735</v>
       </c>
       <c r="P4" t="n">
-        <v>98.8</v>
+        <v>180.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.124099870362662</v>
+        <v>52.33937332448679</v>
       </c>
       <c r="R4" t="n">
-        <v>101.2</v>
+        <v>185.2</v>
       </c>
       <c r="S4" t="n">
-        <v>3.515679166249389</v>
+        <v>48.03082343662245</v>
       </c>
       <c r="T4" t="n">
-        <v>103.4</v>
+        <v>174.6</v>
       </c>
       <c r="U4" t="n">
-        <v>3.9293765408777</v>
+        <v>42.41744923967023</v>
       </c>
       <c r="V4" t="n">
-        <v>104.3</v>
+        <v>207.2</v>
       </c>
       <c r="W4" t="n">
-        <v>4.539823785126467</v>
+        <v>69.10976776114936</v>
       </c>
       <c r="X4" t="n">
-        <v>100.4</v>
+        <v>188</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.26033953682132</v>
+        <v>48.05621707958295</v>
       </c>
       <c r="Z4" t="n">
-        <v>100.2</v>
+        <v>199.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.21428011204396</v>
+        <v>54.88178204103799</v>
       </c>
       <c r="AB4" t="n">
-        <v>78.59999999999999</v>
+        <v>201.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>32.50599944625607</v>
+        <v>37.7804182083788</v>
       </c>
       <c r="AD4" t="n">
-        <v>84.7</v>
+        <v>210.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>30.90323607650176</v>
+        <v>45.95693636438356</v>
       </c>
       <c r="AF4" t="n">
-        <v>71.90000000000001</v>
+        <v>202.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>31.96075718752608</v>
+        <v>52.66393452828985</v>
       </c>
       <c r="AH4" t="n">
-        <v>79.3</v>
+        <v>217.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>33.86163020293028</v>
+        <v>40.78492368510697</v>
       </c>
       <c r="AJ4" t="n">
-        <v>86.3</v>
+        <v>205</v>
       </c>
       <c r="AK4" t="n">
-        <v>33.06372634776667</v>
+        <v>26.96293752542553</v>
       </c>
       <c r="AL4" t="n">
-        <v>66.90000000000001</v>
+        <v>236.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>30.9012944712677</v>
+        <v>36.36770545415258</v>
       </c>
       <c r="AN4" t="n">
-        <v>45.8</v>
+        <v>218.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.227105745132008</v>
+        <v>36.22443926412112</v>
       </c>
       <c r="AP4" t="n">
-        <v>52.2</v>
+        <v>248.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.69652374105946</v>
+        <v>52.50104760859539</v>
       </c>
       <c r="AR4" t="n">
-        <v>53.9</v>
+        <v>228.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>22.1153792642134</v>
+        <v>38.0290678297536</v>
       </c>
       <c r="AT4" t="n">
-        <v>52.1</v>
+        <v>235</v>
       </c>
       <c r="AU4" t="n">
-        <v>19.34657592443686</v>
+        <v>57.44736721556524</v>
       </c>
       <c r="AV4" t="n">
-        <v>52.4</v>
+        <v>237.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>19.25201288177421</v>
+        <v>48.23525681490667</v>
       </c>
       <c r="AX4" t="n">
-        <v>53.2</v>
+        <v>274.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>18.97261183917491</v>
+        <v>67.2321351735909</v>
       </c>
       <c r="AZ4" t="n">
-        <v>47.3</v>
+        <v>217.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.226453160980336</v>
+        <v>38.39127505045906</v>
       </c>
       <c r="BB4" t="n">
-        <v>47.2</v>
+        <v>244.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.6</v>
+        <v>60.22632314860338</v>
       </c>
       <c r="BD4" t="n">
-        <v>48.4</v>
+        <v>227.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.231098884280702</v>
+        <v>49.83412485436059</v>
       </c>
       <c r="BF4" t="n">
-        <v>46.6</v>
+        <v>230.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.498888751680798</v>
+        <v>59.12833500108049</v>
       </c>
       <c r="BH4" t="n">
-        <v>47.6</v>
+        <v>248.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.063595560468865</v>
+        <v>55.57922273655867</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2290.2</v>
+        <v>6078.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>76.34</v>
+        <v>202.6133333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1323,190 +1323,190 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>88.59999999999999</v>
+        <v>141.3</v>
       </c>
       <c r="C5" t="n">
-        <v>22.57077756746542</v>
+        <v>5.367494760127857</v>
       </c>
       <c r="D5" t="n">
-        <v>92.40000000000001</v>
+        <v>142.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2.615339366124404</v>
+        <v>6.738694235532579</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>149.6</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04939015319192</v>
+        <v>7.378346698278686</v>
       </c>
       <c r="H5" t="n">
-        <v>94.59999999999999</v>
+        <v>151.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.469870314579495</v>
+        <v>11.49608629055993</v>
       </c>
       <c r="J5" t="n">
-        <v>93.40000000000001</v>
+        <v>156.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.416609194718914</v>
+        <v>14.83408237809134</v>
       </c>
       <c r="L5" t="n">
-        <v>93.59999999999999</v>
+        <v>146.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.352610922848042</v>
+        <v>7.102112361825882</v>
       </c>
       <c r="N5" t="n">
-        <v>100.1</v>
+        <v>185.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>44.68657516525517</v>
       </c>
       <c r="P5" t="n">
-        <v>100.9</v>
+        <v>182.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.207802986469088</v>
+        <v>50.99450950837747</v>
       </c>
       <c r="R5" t="n">
-        <v>100.8</v>
+        <v>206.9</v>
       </c>
       <c r="S5" t="n">
-        <v>4.331281565541543</v>
+        <v>77.18607387346503</v>
       </c>
       <c r="T5" t="n">
-        <v>105.2</v>
+        <v>173.4</v>
       </c>
       <c r="U5" t="n">
-        <v>3.789459064299283</v>
+        <v>43.77716299624726</v>
       </c>
       <c r="V5" t="n">
-        <v>103.5</v>
+        <v>205</v>
       </c>
       <c r="W5" t="n">
-        <v>3.354101966249685</v>
+        <v>60.83584469702052</v>
       </c>
       <c r="X5" t="n">
-        <v>92.5</v>
+        <v>196.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.98804036885267</v>
+        <v>39.39593887699593</v>
       </c>
       <c r="Z5" t="n">
-        <v>83.2</v>
+        <v>224.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>31.44455437750709</v>
+        <v>73.77777443105748</v>
       </c>
       <c r="AB5" t="n">
-        <v>76.3</v>
+        <v>186.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>31.45170901556861</v>
+        <v>36.1186932211009</v>
       </c>
       <c r="AD5" t="n">
-        <v>101.8</v>
+        <v>199.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>18.24719156473127</v>
+        <v>42.40766440161496</v>
       </c>
       <c r="AF5" t="n">
-        <v>78.7</v>
+        <v>213.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>32.53628743418646</v>
+        <v>33.91002801532314</v>
       </c>
       <c r="AH5" t="n">
-        <v>71.7</v>
+        <v>222.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>32.89088019497198</v>
+        <v>33.82321687835147</v>
       </c>
       <c r="AJ5" t="n">
-        <v>58.7</v>
+        <v>202.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>24.51958400952186</v>
+        <v>29.71262357988605</v>
       </c>
       <c r="AL5" t="n">
-        <v>67</v>
+        <v>245.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>31.05157000861631</v>
+        <v>53.31875842515465</v>
       </c>
       <c r="AN5" t="n">
-        <v>53.8</v>
+        <v>223.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>21.4653208687874</v>
+        <v>53.70437598557496</v>
       </c>
       <c r="AP5" t="n">
-        <v>54.1</v>
+        <v>234.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20.06215342379776</v>
+        <v>46.67590384770283</v>
       </c>
       <c r="AR5" t="n">
-        <v>45.8</v>
+        <v>236.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.785677655436824</v>
+        <v>56.6467121729055</v>
       </c>
       <c r="AT5" t="n">
-        <v>54.3</v>
+        <v>241.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>19.39613363534083</v>
+        <v>41.32178602141974</v>
       </c>
       <c r="AV5" t="n">
-        <v>46.1</v>
+        <v>255.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.640121946685673</v>
+        <v>71.66931002877033</v>
       </c>
       <c r="AX5" t="n">
-        <v>44.4</v>
+        <v>257.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.576819745345025</v>
+        <v>69.92167046059468</v>
       </c>
       <c r="AZ5" t="n">
-        <v>45.6</v>
+        <v>248.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.690724809414742</v>
+        <v>50.73351949155509</v>
       </c>
       <c r="BB5" t="n">
-        <v>46.5</v>
+        <v>293.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.129164564412516</v>
+        <v>67.40185457389137</v>
       </c>
       <c r="BD5" t="n">
-        <v>49.2</v>
+        <v>223.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.925747767665559</v>
+        <v>46.34101854728702</v>
       </c>
       <c r="BF5" t="n">
-        <v>47.3</v>
+        <v>230.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.49428104193123</v>
+        <v>50.07444458004502</v>
       </c>
       <c r="BH5" t="n">
-        <v>46.2</v>
+        <v>220.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.959729717389748</v>
+        <v>42.32599673959256</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2231.299999999999</v>
+        <v>6195.099999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>74.37666666666664</v>
+        <v>206.5033333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1514,190 +1514,190 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>94.3</v>
+        <v>141.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1</v>
+        <v>9.162968951164245</v>
       </c>
       <c r="D6" t="n">
-        <v>94.7</v>
+        <v>140.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.067572330035594</v>
+        <v>6.3118935352238</v>
       </c>
       <c r="F6" t="n">
-        <v>93.3</v>
+        <v>144</v>
       </c>
       <c r="G6" t="n">
-        <v>4.148493702538308</v>
+        <v>5.440588203494177</v>
       </c>
       <c r="H6" t="n">
-        <v>93.8</v>
+        <v>144.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>4.801041553663121</v>
       </c>
       <c r="J6" t="n">
-        <v>93.8</v>
+        <v>161.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.124099870362662</v>
+        <v>38.32179536503998</v>
       </c>
       <c r="L6" t="n">
-        <v>95.7</v>
+        <v>166.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.436568055487916</v>
+        <v>32.93994535514593</v>
       </c>
       <c r="N6" t="n">
-        <v>98</v>
+        <v>166.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.857983120596447</v>
+        <v>37.20806364217305</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>153.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.898979485566356</v>
+        <v>7.039886362719216</v>
       </c>
       <c r="R6" t="n">
-        <v>100.1</v>
+        <v>176.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.562302626111375</v>
+        <v>46.69743033615448</v>
       </c>
       <c r="T6" t="n">
-        <v>96.7</v>
+        <v>166.3</v>
       </c>
       <c r="U6" t="n">
-        <v>17.44734936888695</v>
+        <v>21.64278170661064</v>
       </c>
       <c r="V6" t="n">
-        <v>91.2</v>
+        <v>186.9</v>
       </c>
       <c r="W6" t="n">
-        <v>22.15310362003482</v>
+        <v>51.84679353634128</v>
       </c>
       <c r="X6" t="n">
-        <v>94.40000000000001</v>
+        <v>195.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.60937328401459</v>
+        <v>52.95243148336061</v>
       </c>
       <c r="Z6" t="n">
-        <v>95.5</v>
+        <v>209</v>
       </c>
       <c r="AA6" t="n">
-        <v>26.36380093992518</v>
+        <v>47.54576742466147</v>
       </c>
       <c r="AB6" t="n">
-        <v>64.5</v>
+        <v>215.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>28.95945441475029</v>
+        <v>53.38389270182533</v>
       </c>
       <c r="AD6" t="n">
-        <v>77.40000000000001</v>
+        <v>200.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>31.5220557705236</v>
+        <v>41.8197321846996</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.5</v>
+        <v>195.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>28.77585793681919</v>
+        <v>31.01999355254607</v>
       </c>
       <c r="AH6" t="n">
-        <v>70.8</v>
+        <v>194.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>30.62613263211664</v>
+        <v>19.36724038163414</v>
       </c>
       <c r="AJ6" t="n">
-        <v>59.2</v>
+        <v>249.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>26.96961252966012</v>
+        <v>67.82595373454029</v>
       </c>
       <c r="AL6" t="n">
-        <v>58.9</v>
+        <v>222.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>24.87749987438448</v>
+        <v>49.43844657753721</v>
       </c>
       <c r="AN6" t="n">
-        <v>53.7</v>
+        <v>228.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.9055857206627</v>
+        <v>39.25862962458063</v>
       </c>
       <c r="AP6" t="n">
-        <v>65.8</v>
+        <v>240.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>30.53457057173066</v>
+        <v>61.5279611233787</v>
       </c>
       <c r="AR6" t="n">
-        <v>58.2</v>
+        <v>241.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>26.25566605515846</v>
+        <v>58.43834357679896</v>
       </c>
       <c r="AT6" t="n">
-        <v>52.9</v>
+        <v>239.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>20.56915165970634</v>
+        <v>46.1615640982842</v>
       </c>
       <c r="AV6" t="n">
-        <v>46.9</v>
+        <v>224.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.813835714721705</v>
+        <v>52.92078986560953</v>
       </c>
       <c r="AX6" t="n">
-        <v>46.4</v>
+        <v>223</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.374868417407583</v>
+        <v>45.27692569068709</v>
       </c>
       <c r="AZ6" t="n">
-        <v>45.3</v>
+        <v>236</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.86530975637888</v>
+        <v>57.47869170396974</v>
       </c>
       <c r="BB6" t="n">
-        <v>47.5</v>
+        <v>237.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.376972864800943</v>
+        <v>61.03408883566625</v>
       </c>
       <c r="BD6" t="n">
-        <v>50.9</v>
+        <v>250.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>13.80905500025255</v>
+        <v>51.7966215114461</v>
       </c>
       <c r="BF6" t="n">
-        <v>45.8</v>
+        <v>267.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.271563338320109</v>
+        <v>60.65509047062744</v>
       </c>
       <c r="BH6" t="n">
-        <v>46.5</v>
+        <v>259.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.746424919657298</v>
+        <v>74.50134226978733</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2196.700000000001</v>
+        <v>6078.3</v>
       </c>
       <c r="BK6" t="n">
-        <v>73.22333333333337</v>
+        <v>202.61</v>
       </c>
     </row>
     <row r="7">
@@ -1705,190 +1705,190 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>144.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.255764119219941</v>
+        <v>5.491812087098393</v>
       </c>
       <c r="D7" t="n">
-        <v>94.8</v>
+        <v>143.9</v>
       </c>
       <c r="E7" t="n">
-        <v>2.925747767665559</v>
+        <v>4.887739763939975</v>
       </c>
       <c r="F7" t="n">
-        <v>94.40000000000001</v>
+        <v>146.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.555277766926235</v>
+        <v>8.121576201698781</v>
       </c>
       <c r="H7" t="n">
-        <v>93.59999999999999</v>
+        <v>148.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.374868417407583</v>
+        <v>7.184010022264724</v>
       </c>
       <c r="J7" t="n">
-        <v>95.2</v>
+        <v>152.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.993325909419153</v>
+        <v>16.87720355983183</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>149.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.255764119219941</v>
+        <v>9.833107342035884</v>
       </c>
       <c r="N7" t="n">
-        <v>98</v>
+        <v>154.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.949358868961793</v>
+        <v>7.794870107962031</v>
       </c>
       <c r="P7" t="n">
-        <v>97.5</v>
+        <v>183.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05585995813465</v>
+        <v>55.83690535837387</v>
       </c>
       <c r="R7" t="n">
-        <v>99.5</v>
+        <v>182.8</v>
       </c>
       <c r="S7" t="n">
-        <v>3.170173496829472</v>
+        <v>52.99962264016603</v>
       </c>
       <c r="T7" t="n">
-        <v>104.9</v>
+        <v>192.9</v>
       </c>
       <c r="U7" t="n">
-        <v>2.50798724079689</v>
+        <v>61.3603292038105</v>
       </c>
       <c r="V7" t="n">
-        <v>98.2</v>
+        <v>196.9</v>
       </c>
       <c r="W7" t="n">
-        <v>17.80337046741431</v>
+        <v>66.34975508620961</v>
       </c>
       <c r="X7" t="n">
-        <v>100.8</v>
+        <v>231.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.33466661818534</v>
+        <v>74.66163673534086</v>
       </c>
       <c r="Z7" t="n">
-        <v>96.2</v>
+        <v>227</v>
       </c>
       <c r="AA7" t="n">
-        <v>25.41574315262098</v>
+        <v>73.29802180141017</v>
       </c>
       <c r="AB7" t="n">
-        <v>83</v>
+        <v>217.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>30.54832237619605</v>
+        <v>49.88396535962232</v>
       </c>
       <c r="AD7" t="n">
-        <v>64.7</v>
+        <v>205.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>27.56827887264636</v>
+        <v>47.67221412940666</v>
       </c>
       <c r="AF7" t="n">
-        <v>71.3</v>
+        <v>204.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>32.17157130138346</v>
+        <v>42.38584669438609</v>
       </c>
       <c r="AH7" t="n">
-        <v>66.59999999999999</v>
+        <v>193</v>
       </c>
       <c r="AI7" t="n">
-        <v>28.94546596619236</v>
+        <v>24.6414285300183</v>
       </c>
       <c r="AJ7" t="n">
-        <v>72.5</v>
+        <v>213.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>32.49384557112315</v>
+        <v>45.88725313199735</v>
       </c>
       <c r="AL7" t="n">
-        <v>47.3</v>
+        <v>204</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.72213151776324</v>
+        <v>47.50789408087881</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.6</v>
+        <v>237.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.496662954709577</v>
+        <v>56.91607857187633</v>
       </c>
       <c r="AP7" t="n">
-        <v>52.2</v>
+        <v>225.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19.30699355156053</v>
+        <v>53.88701142204864</v>
       </c>
       <c r="AR7" t="n">
-        <v>60.4</v>
+        <v>222</v>
       </c>
       <c r="AS7" t="n">
-        <v>26.08907817459252</v>
+        <v>44.73030292765744</v>
       </c>
       <c r="AT7" t="n">
-        <v>52.1</v>
+        <v>236.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>21.37498538011196</v>
+        <v>47.92535863193931</v>
       </c>
       <c r="AV7" t="n">
-        <v>53.1</v>
+        <v>221.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>19.1020941260376</v>
+        <v>28.06706254669341</v>
       </c>
       <c r="AX7" t="n">
-        <v>50.2</v>
+        <v>222.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.42081828468829</v>
+        <v>64.57871166259048</v>
       </c>
       <c r="AZ7" t="n">
-        <v>47.5</v>
+        <v>223.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.729468812791236</v>
+        <v>51.32211998738946</v>
       </c>
       <c r="BB7" t="n">
-        <v>45.5</v>
+        <v>243.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.354101966249685</v>
+        <v>66.73409922970414</v>
       </c>
       <c r="BD7" t="n">
-        <v>46.6</v>
+        <v>237.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.497999199359359</v>
+        <v>50.52771516702492</v>
       </c>
       <c r="BF7" t="n">
-        <v>47.4</v>
+        <v>230.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.720215047547655</v>
+        <v>44.04043596514457</v>
       </c>
       <c r="BH7" t="n">
-        <v>45.8</v>
+        <v>256.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.271563338320109</v>
+        <v>58.28799190227778</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2215.9</v>
+        <v>6049.199999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>73.86333333333332</v>
+        <v>201.64</v>
       </c>
     </row>
     <row r="8">
@@ -1896,190 +1896,190 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>87.3</v>
+        <v>141.1</v>
       </c>
       <c r="C8" t="n">
-        <v>21.50837046361253</v>
+        <v>7.841555968046137</v>
       </c>
       <c r="D8" t="n">
-        <v>93.5</v>
+        <v>141</v>
       </c>
       <c r="E8" t="n">
-        <v>3.138470965295043</v>
+        <v>5.176871642217914</v>
       </c>
       <c r="F8" t="n">
-        <v>94.2</v>
+        <v>147.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3.187475490101845</v>
+        <v>5.122499389946279</v>
       </c>
       <c r="H8" t="n">
-        <v>93.59999999999999</v>
+        <v>150.9</v>
       </c>
       <c r="I8" t="n">
-        <v>3.168595903550972</v>
+        <v>7.133722730804723</v>
       </c>
       <c r="J8" t="n">
-        <v>95.3</v>
+        <v>152</v>
       </c>
       <c r="K8" t="n">
-        <v>2.147091055358389</v>
+        <v>20.96187014557623</v>
       </c>
       <c r="L8" t="n">
-        <v>94.40000000000001</v>
+        <v>159.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.764054992217051</v>
+        <v>33.39700585381869</v>
       </c>
       <c r="N8" t="n">
-        <v>96.5</v>
+        <v>151.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.981205847478877</v>
+        <v>6.374950980203691</v>
       </c>
       <c r="P8" t="n">
-        <v>99.59999999999999</v>
+        <v>195</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.608687448721165</v>
+        <v>55.27386362468251</v>
       </c>
       <c r="R8" t="n">
-        <v>93.8</v>
+        <v>172.8</v>
       </c>
       <c r="S8" t="n">
-        <v>16.4</v>
+        <v>39.03536857773986</v>
       </c>
       <c r="T8" t="n">
-        <v>102.7</v>
+        <v>174.2</v>
       </c>
       <c r="U8" t="n">
-        <v>4.360045871318328</v>
+        <v>51.9207087779048</v>
       </c>
       <c r="V8" t="n">
-        <v>99.7</v>
+        <v>185.1</v>
       </c>
       <c r="W8" t="n">
-        <v>18.75659883880871</v>
+        <v>66.47774063549392</v>
       </c>
       <c r="X8" t="n">
-        <v>93.8</v>
+        <v>215.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>25.22617688037567</v>
+        <v>91.33591845489921</v>
       </c>
       <c r="Z8" t="n">
-        <v>100.6</v>
+        <v>182.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.99578900704048</v>
+        <v>26.75369133409444</v>
       </c>
       <c r="AB8" t="n">
-        <v>95.7</v>
+        <v>191.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>26.22994471972825</v>
+        <v>60.34243946013453</v>
       </c>
       <c r="AD8" t="n">
-        <v>103.6</v>
+        <v>199.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>18.90608367695436</v>
+        <v>37.45250325412174</v>
       </c>
       <c r="AF8" t="n">
-        <v>97.40000000000001</v>
+        <v>224.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>26.32565288839006</v>
+        <v>56.77930961186478</v>
       </c>
       <c r="AH8" t="n">
-        <v>64.2</v>
+        <v>208.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>30.10581339210087</v>
+        <v>35.49943661524785</v>
       </c>
       <c r="AJ8" t="n">
-        <v>59.2</v>
+        <v>217.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>26.99555518969743</v>
+        <v>32.73056675341874</v>
       </c>
       <c r="AL8" t="n">
-        <v>59.1</v>
+        <v>224.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>26.99055390317139</v>
+        <v>57.15671439122442</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.7</v>
+        <v>224.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>26.21087560536656</v>
+        <v>46.29643614793692</v>
       </c>
       <c r="AP8" t="n">
-        <v>53.8</v>
+        <v>221.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19.4566184112245</v>
+        <v>53.15298674580761</v>
       </c>
       <c r="AR8" t="n">
-        <v>45.9</v>
+        <v>246.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.86815416922694</v>
+        <v>49.88346419405934</v>
       </c>
       <c r="AT8" t="n">
-        <v>59.6</v>
+        <v>259.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>28.06136133547337</v>
+        <v>53.79786241106611</v>
       </c>
       <c r="AV8" t="n">
-        <v>45.3</v>
+        <v>221.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.002498439450079</v>
+        <v>39.47467542615139</v>
       </c>
       <c r="AX8" t="n">
-        <v>44.3</v>
+        <v>246.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.68514431641951</v>
+        <v>48.79600393474859</v>
       </c>
       <c r="AZ8" t="n">
-        <v>46.6</v>
+        <v>261.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.107130750570548</v>
+        <v>67.32971112369339</v>
       </c>
       <c r="BB8" t="n">
-        <v>47</v>
+        <v>248.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.898275349237888</v>
+        <v>64.77221626592686</v>
       </c>
       <c r="BD8" t="n">
-        <v>45.5</v>
+        <v>225.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.565247584249853</v>
+        <v>50.12594138766872</v>
       </c>
       <c r="BF8" t="n">
-        <v>46.7</v>
+        <v>236.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.531797780234433</v>
+        <v>67.70531736872667</v>
       </c>
       <c r="BH8" t="n">
-        <v>48.3</v>
+        <v>219.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.561797891182818</v>
+        <v>38.68966270207069</v>
       </c>
       <c r="BJ8" t="n">
-        <v>2265.9</v>
+        <v>6045.7</v>
       </c>
       <c r="BK8" t="n">
-        <v>75.53</v>
+        <v>201.5233333333333</v>
       </c>
     </row>
     <row r="9">
@@ -2087,190 +2087,190 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>93.8</v>
+        <v>140.1</v>
       </c>
       <c r="C9" t="n">
-        <v>2.959729717389749</v>
+        <v>6.024118192731614</v>
       </c>
       <c r="D9" t="n">
-        <v>92.09999999999999</v>
+        <v>142.4</v>
       </c>
       <c r="E9" t="n">
-        <v>2.343074902771996</v>
+        <v>5.817215828899594</v>
       </c>
       <c r="F9" t="n">
-        <v>93.3</v>
+        <v>147.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.226453160980336</v>
+        <v>4.758150901348127</v>
       </c>
       <c r="H9" t="n">
-        <v>94.3</v>
+        <v>149</v>
       </c>
       <c r="I9" t="n">
-        <v>2.147091055358389</v>
+        <v>5.882176467941097</v>
       </c>
       <c r="J9" t="n">
-        <v>96.5</v>
+        <v>161.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.293933818400121</v>
+        <v>29.21711826994579</v>
       </c>
       <c r="L9" t="n">
-        <v>97.09999999999999</v>
+        <v>148.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.144837038703278</v>
+        <v>8.795453370918409</v>
       </c>
       <c r="N9" t="n">
-        <v>98.90000000000001</v>
+        <v>179.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.920937271229854</v>
+        <v>47.58823383988945</v>
       </c>
       <c r="P9" t="n">
-        <v>99.3</v>
+        <v>177.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.356886030125128</v>
+        <v>41.24609072384921</v>
       </c>
       <c r="R9" t="n">
-        <v>100.8</v>
+        <v>183.1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.135415650406262</v>
+        <v>55.10979949156048</v>
       </c>
       <c r="T9" t="n">
-        <v>104.7</v>
+        <v>154.8</v>
       </c>
       <c r="U9" t="n">
-        <v>4.473253849269008</v>
+        <v>5.528109984434101</v>
       </c>
       <c r="V9" t="n">
-        <v>93.90000000000001</v>
+        <v>180.6</v>
       </c>
       <c r="W9" t="n">
-        <v>23.5008510484195</v>
+        <v>51.3988326715695</v>
       </c>
       <c r="X9" t="n">
-        <v>94.90000000000001</v>
+        <v>185.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.0896392959325</v>
+        <v>58.8883689704512</v>
       </c>
       <c r="Z9" t="n">
-        <v>96.8</v>
+        <v>211.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>25.64683216305671</v>
+        <v>55.57193536309492</v>
       </c>
       <c r="AB9" t="n">
-        <v>96.90000000000001</v>
+        <v>229.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.74276597415281</v>
+        <v>44.38794881496553</v>
       </c>
       <c r="AD9" t="n">
-        <v>90.7</v>
+        <v>187.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>28.43606864529624</v>
+        <v>28.85983367935443</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.59999999999999</v>
+        <v>193.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>30.00066665925942</v>
+        <v>41.75032934001838</v>
       </c>
       <c r="AH9" t="n">
-        <v>65.2</v>
+        <v>206.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>31.50809419815803</v>
+        <v>42.63390669408564</v>
       </c>
       <c r="AJ9" t="n">
-        <v>52.8</v>
+        <v>200.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>20.87965516956638</v>
+        <v>28.88615585362649</v>
       </c>
       <c r="AL9" t="n">
-        <v>59.5</v>
+        <v>212.9</v>
       </c>
       <c r="AM9" t="n">
-        <v>27.28827587078377</v>
+        <v>40.13340254700566</v>
       </c>
       <c r="AN9" t="n">
-        <v>52.8</v>
+        <v>218</v>
       </c>
       <c r="AO9" t="n">
-        <v>20.46362626711112</v>
+        <v>49.43278264471868</v>
       </c>
       <c r="AP9" t="n">
-        <v>46.1</v>
+        <v>232.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.757839583124694</v>
+        <v>51.53067047885172</v>
       </c>
       <c r="AR9" t="n">
-        <v>59.1</v>
+        <v>230.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>27.48253991173305</v>
+        <v>42.39622624715553</v>
       </c>
       <c r="AT9" t="n">
-        <v>47</v>
+        <v>270.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.82842712474619</v>
+        <v>55.02944666267325</v>
       </c>
       <c r="AV9" t="n">
-        <v>47.4</v>
+        <v>231</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.835489375751565</v>
+        <v>57.87054518492115</v>
       </c>
       <c r="AX9" t="n">
-        <v>46.3</v>
+        <v>227.3</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.791647286716892</v>
+        <v>59.78135160733655</v>
       </c>
       <c r="AZ9" t="n">
-        <v>46.8</v>
+        <v>264.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.08806130178211</v>
+        <v>66.67263306634889</v>
       </c>
       <c r="BB9" t="n">
-        <v>47.8</v>
+        <v>226.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.4</v>
+        <v>43.26673086795442</v>
       </c>
       <c r="BD9" t="n">
-        <v>47.9</v>
+        <v>242</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.323193264243457</v>
+        <v>45.00666617291265</v>
       </c>
       <c r="BF9" t="n">
-        <v>47.5</v>
+        <v>246.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>66.03854934808911</v>
       </c>
       <c r="BH9" t="n">
-        <v>47.7</v>
+        <v>233.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.647640458974745</v>
+        <v>54.67403405639646</v>
       </c>
       <c r="BJ9" t="n">
-        <v>2230.5</v>
+        <v>6014.1</v>
       </c>
       <c r="BK9" t="n">
-        <v>74.34999999999999</v>
+        <v>200.47</v>
       </c>
     </row>
     <row r="10">
@@ -2278,190 +2278,190 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>94.40000000000001</v>
+        <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>3.903844259188627</v>
+        <v>6.033241251599343</v>
       </c>
       <c r="D10" t="n">
-        <v>93.5</v>
+        <v>144.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3.170173496829472</v>
+        <v>8.487638069569178</v>
       </c>
       <c r="F10" t="n">
-        <v>95.2</v>
+        <v>147.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.487119154832539</v>
+        <v>5.817215828899595</v>
       </c>
       <c r="H10" t="n">
-        <v>96</v>
+        <v>154.9</v>
       </c>
       <c r="I10" t="n">
-        <v>2.645751311064591</v>
+        <v>12.27558552574988</v>
       </c>
       <c r="J10" t="n">
-        <v>93.90000000000001</v>
+        <v>145.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.586503431275513</v>
+        <v>5.642694391866354</v>
       </c>
       <c r="L10" t="n">
-        <v>96.2</v>
+        <v>178.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.142463035441596</v>
+        <v>39.86677814923097</v>
       </c>
       <c r="N10" t="n">
-        <v>97.09999999999999</v>
+        <v>158.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.419064199455752</v>
+        <v>33.23266465392145</v>
       </c>
       <c r="P10" t="n">
-        <v>99</v>
+        <v>168.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.863564212655271</v>
+        <v>21.51487857274589</v>
       </c>
       <c r="R10" t="n">
-        <v>103.7</v>
+        <v>169.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.243819034784589</v>
+        <v>48.34004551094258</v>
       </c>
       <c r="T10" t="n">
-        <v>97.09999999999999</v>
+        <v>193.6</v>
       </c>
       <c r="U10" t="n">
-        <v>17.56388339747221</v>
+        <v>69.31839582679333</v>
       </c>
       <c r="V10" t="n">
-        <v>98</v>
+        <v>248</v>
       </c>
       <c r="W10" t="n">
-        <v>17.62384748004816</v>
+        <v>76.82577692415482</v>
       </c>
       <c r="X10" t="n">
-        <v>82.3</v>
+        <v>178.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>29.31569545482419</v>
+        <v>45.22222904722853</v>
       </c>
       <c r="Z10" t="n">
-        <v>107.6</v>
+        <v>220.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.624807680927192</v>
+        <v>56.87389559367286</v>
       </c>
       <c r="AB10" t="n">
-        <v>64</v>
+        <v>186.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>29.56687335515881</v>
+        <v>25.67800615312645</v>
       </c>
       <c r="AD10" t="n">
-        <v>76.7</v>
+        <v>231.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>31.68296072023573</v>
+        <v>50.13741118167152</v>
       </c>
       <c r="AF10" t="n">
-        <v>76.3</v>
+        <v>202.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.35753389861471</v>
+        <v>31.53474274510575</v>
       </c>
       <c r="AH10" t="n">
-        <v>75.2</v>
+        <v>235</v>
       </c>
       <c r="AI10" t="n">
-        <v>34.17250356646407</v>
+        <v>37.78624088209887</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65.09999999999999</v>
+        <v>220.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>30.95302893094632</v>
+        <v>48.1361610434401</v>
       </c>
       <c r="AL10" t="n">
-        <v>52.3</v>
+        <v>195.4</v>
       </c>
       <c r="AM10" t="n">
-        <v>18.62820442232691</v>
+        <v>25.60156245231919</v>
       </c>
       <c r="AN10" t="n">
-        <v>66</v>
+        <v>226.9</v>
       </c>
       <c r="AO10" t="n">
-        <v>29.53980365540706</v>
+        <v>48.23992122713303</v>
       </c>
       <c r="AP10" t="n">
-        <v>53.2</v>
+        <v>218.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20.37056700241797</v>
+        <v>57.6787655901199</v>
       </c>
       <c r="AR10" t="n">
-        <v>65.8</v>
+        <v>225</v>
       </c>
       <c r="AS10" t="n">
-        <v>30.3736728105114</v>
+        <v>63.79498412884825</v>
       </c>
       <c r="AT10" t="n">
-        <v>45.6</v>
+        <v>256</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.0591260281974</v>
+        <v>62.5347903170707</v>
       </c>
       <c r="AV10" t="n">
-        <v>46.6</v>
+        <v>252.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.835489375751565</v>
+        <v>69.69684354402285</v>
       </c>
       <c r="AX10" t="n">
-        <v>45.8</v>
+        <v>241.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.536229149573722</v>
+        <v>70.20797675478192</v>
       </c>
       <c r="AZ10" t="n">
-        <v>45.8</v>
+        <v>249.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.357965224510319</v>
+        <v>54.12291566425446</v>
       </c>
       <c r="BB10" t="n">
-        <v>46.6</v>
+        <v>243</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.152107898405339</v>
+        <v>59.09483903015558</v>
       </c>
       <c r="BD10" t="n">
-        <v>48</v>
+        <v>218.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.376388603226827</v>
+        <v>39.50392385573868</v>
       </c>
       <c r="BF10" t="n">
-        <v>48.9</v>
+        <v>242.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.635730794599704</v>
+        <v>54.51018253500899</v>
       </c>
       <c r="BH10" t="n">
-        <v>47.4</v>
+        <v>221.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.072458299147443</v>
+        <v>36.81521424628682</v>
       </c>
       <c r="BJ10" t="n">
-        <v>2223.3</v>
+        <v>6115.799999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>74.10999999999999</v>
+        <v>203.86</v>
       </c>
     </row>
     <row r="11">
@@ -2469,190 +2469,190 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>94.8</v>
+        <v>139.6</v>
       </c>
       <c r="C11" t="n">
-        <v>4.377213725647858</v>
+        <v>5.219195340279955</v>
       </c>
       <c r="D11" t="n">
-        <v>93.2</v>
+        <v>145.4</v>
       </c>
       <c r="E11" t="n">
-        <v>3.370459909270544</v>
+        <v>4.31740662898458</v>
       </c>
       <c r="F11" t="n">
-        <v>94.59999999999999</v>
+        <v>142.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.685229954635272</v>
+        <v>3.522782990761708</v>
       </c>
       <c r="H11" t="n">
-        <v>94.90000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.211334438749598</v>
+        <v>5.481788029466299</v>
       </c>
       <c r="J11" t="n">
-        <v>94.59999999999999</v>
+        <v>146.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1.854723699099141</v>
+        <v>6.220128616033595</v>
       </c>
       <c r="L11" t="n">
-        <v>95.59999999999999</v>
+        <v>153.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.072458299147443</v>
+        <v>7.632168761236874</v>
       </c>
       <c r="N11" t="n">
-        <v>97.40000000000001</v>
+        <v>155.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.615339366124404</v>
+        <v>11.27342006668784</v>
       </c>
       <c r="P11" t="n">
-        <v>97.8</v>
+        <v>163.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.891366458960192</v>
+        <v>18.89867720238642</v>
       </c>
       <c r="R11" t="n">
-        <v>104.2</v>
+        <v>176.4</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1182520563948</v>
+        <v>40.88814008976197</v>
       </c>
       <c r="T11" t="n">
-        <v>101.1</v>
+        <v>160.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.808914381037628</v>
+        <v>9.495261976375375</v>
       </c>
       <c r="V11" t="n">
-        <v>85.8</v>
+        <v>194.6</v>
       </c>
       <c r="W11" t="n">
-        <v>26.47942597565136</v>
+        <v>55.03308096045505</v>
       </c>
       <c r="X11" t="n">
-        <v>95.09999999999999</v>
+        <v>203.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>24.65542536643812</v>
+        <v>77.08929886826057</v>
       </c>
       <c r="Z11" t="n">
-        <v>94.5</v>
+        <v>206.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>24.68704113497606</v>
+        <v>53.80975747947578</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.90000000000001</v>
+        <v>189.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.46546681292138</v>
+        <v>30.40082235729817</v>
       </c>
       <c r="AD11" t="n">
-        <v>84.2</v>
+        <v>193.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>31.04126286090822</v>
+        <v>29.72557821136538</v>
       </c>
       <c r="AF11" t="n">
-        <v>79.3</v>
+        <v>225</v>
       </c>
       <c r="AG11" t="n">
-        <v>31.57863201596928</v>
+        <v>52.00576891076604</v>
       </c>
       <c r="AH11" t="n">
-        <v>73.8</v>
+        <v>205.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>33.14754892899322</v>
+        <v>25.22399651125888</v>
       </c>
       <c r="AJ11" t="n">
-        <v>79.40000000000001</v>
+        <v>229</v>
       </c>
       <c r="AK11" t="n">
-        <v>32.50907565588416</v>
+        <v>58.55083261577072</v>
       </c>
       <c r="AL11" t="n">
-        <v>53.1</v>
+        <v>222.4</v>
       </c>
       <c r="AM11" t="n">
-        <v>21.05920226409348</v>
+        <v>58.04687760767154</v>
       </c>
       <c r="AN11" t="n">
-        <v>46</v>
+        <v>261.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.61245154965971</v>
+        <v>65.0319921269524</v>
       </c>
       <c r="AP11" t="n">
-        <v>53.4</v>
+        <v>243.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19.63262590689284</v>
+        <v>60.06704587375677</v>
       </c>
       <c r="AR11" t="n">
-        <v>61.2</v>
+        <v>235.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>26.94735608552349</v>
+        <v>63.51606096098844</v>
       </c>
       <c r="AT11" t="n">
-        <v>54.2</v>
+        <v>226.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>21.42801904049929</v>
+        <v>55.79283108070426</v>
       </c>
       <c r="AV11" t="n">
-        <v>45.9</v>
+        <v>221.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.57797338380595</v>
+        <v>54.76714343472736</v>
       </c>
       <c r="AX11" t="n">
-        <v>45.6</v>
+        <v>237.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.289104628451919</v>
+        <v>61.6383809002151</v>
       </c>
       <c r="AZ11" t="n">
-        <v>46.8</v>
+        <v>210.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.059411708155671</v>
+        <v>39.40672531434197</v>
       </c>
       <c r="BB11" t="n">
-        <v>51.6</v>
+        <v>229.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.77971582947385</v>
+        <v>58.32846646364021</v>
       </c>
       <c r="BD11" t="n">
-        <v>48.2</v>
+        <v>242</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.993325909419153</v>
+        <v>47.12748667179272</v>
       </c>
       <c r="BF11" t="n">
-        <v>46.1</v>
+        <v>256.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.961060464067672</v>
+        <v>63.15251380586524</v>
       </c>
       <c r="BH11" t="n">
-        <v>49.3</v>
+        <v>239.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.822302970723279</v>
+        <v>57.69263384523192</v>
       </c>
       <c r="BJ11" t="n">
-        <v>2258.6</v>
+        <v>6000.400000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>75.28666666666666</v>
+        <v>200.0133333333333</v>
       </c>
     </row>
   </sheetData>
